--- a/data/提出資料/130_鎌田緑保護会_構成員名簿_20260721.xlsx
+++ b/data/提出資料/130_鎌田緑保護会_構成員名簿_20260721.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taros\Documents\Koyu\dev\tamokuteki_kinouhakki_sokushin_erp\data\提出資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12B05555-41D5-4004-84C8-D35F2F0BF3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF892C74-BD0C-43FC-A480-A99BB4961AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22956" yWindow="2304" windowWidth="21816" windowHeight="22572" xr2:uid="{9E259925-20DE-48A5-92CC-CC78E8D535DE}"/>
+    <workbookView xWindow="29136" yWindow="1332" windowWidth="17028" windowHeight="23040" xr2:uid="{9E259925-20DE-48A5-92CC-CC78E8D535DE}"/>
   </bookViews>
   <sheets>
     <sheet name="130_鎌田緑保護会" sheetId="1" r:id="rId1"/>
@@ -373,9 +373,6 @@
     <t xml:space="preserve">柏崎市西山町鎌田７６０ </t>
   </si>
   <si>
-    <t>藤井恒夫</t>
-  </si>
-  <si>
     <t xml:space="preserve">柏崎市西山町鎌田１１４１ </t>
   </si>
   <si>
@@ -846,6 +843,10 @@
   </si>
   <si>
     <t xml:space="preserve">柏崎市西山町鎌田１１７３－１ </t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>藤井恒雄</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
@@ -1495,7 +1496,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1592,9 +1593,6 @@
     <xf numFmtId="0" fontId="22" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1988,7 +1986,7 @@
         <v>24</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
@@ -2052,7 +2050,7 @@
         <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>31</v>
@@ -2133,7 +2131,7 @@
         <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>38</v>
@@ -2158,7 +2156,7 @@
         <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>36</v>
@@ -2187,7 +2185,7 @@
         <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>41</v>
@@ -2264,7 +2262,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>44</v>
@@ -2472,13 +2470,13 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>44</v>
@@ -2489,13 +2487,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>44</v>
@@ -2506,13 +2504,13 @@
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>44</v>
@@ -2523,13 +2521,13 @@
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>31</v>
@@ -2540,13 +2538,13 @@
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>74</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>31</v>
@@ -2557,13 +2555,13 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>31</v>
@@ -2574,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>31</v>
@@ -2591,13 +2589,13 @@
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>31</v>
@@ -2608,13 +2606,13 @@
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>31</v>
@@ -2625,13 +2623,13 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>31</v>
@@ -2642,13 +2640,13 @@
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>31</v>
@@ -2659,13 +2657,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>31</v>
@@ -2676,13 +2674,13 @@
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>44</v>
@@ -2693,13 +2691,13 @@
         <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>44</v>
@@ -2710,13 +2708,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>31</v>
@@ -2727,13 +2725,13 @@
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>44</v>
@@ -2744,13 +2742,13 @@
         <v>36</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>44</v>
@@ -2761,13 +2759,13 @@
         <v>37</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>44</v>
@@ -2778,13 +2776,13 @@
         <v>38</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>44</v>
@@ -2795,13 +2793,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>44</v>
@@ -2812,13 +2810,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>44</v>
@@ -2829,13 +2827,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>44</v>
@@ -2846,13 +2844,13 @@
         <v>42</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>44</v>
@@ -2863,13 +2861,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>44</v>
@@ -2880,13 +2878,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>44</v>
@@ -2897,13 +2895,13 @@
         <v>45</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>44</v>
@@ -2914,13 +2912,13 @@
         <v>46</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>44</v>
@@ -2931,13 +2929,13 @@
         <v>47</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>44</v>
@@ -2948,13 +2946,13 @@
         <v>48</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>44</v>
@@ -2965,13 +2963,13 @@
         <v>49</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>44</v>
@@ -2982,13 +2980,13 @@
         <v>50</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>44</v>
@@ -2999,13 +2997,13 @@
         <v>51</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>44</v>
@@ -3016,13 +3014,13 @@
         <v>52</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>44</v>
@@ -3033,13 +3031,13 @@
         <v>53</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>44</v>
@@ -3050,13 +3048,13 @@
         <v>54</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>44</v>
@@ -3067,13 +3065,13 @@
         <v>55</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>44</v>
@@ -3084,13 +3082,13 @@
         <v>56</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>44</v>
@@ -3101,13 +3099,13 @@
         <v>57</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>44</v>
@@ -3118,13 +3116,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>44</v>
@@ -3135,13 +3133,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>44</v>
@@ -3152,13 +3150,13 @@
         <v>60</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>44</v>
@@ -3169,13 +3167,13 @@
         <v>61</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>44</v>
@@ -3186,13 +3184,13 @@
         <v>62</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>44</v>
@@ -3203,13 +3201,13 @@
         <v>63</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>44</v>
@@ -3220,13 +3218,13 @@
         <v>64</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>44</v>
@@ -3237,13 +3235,13 @@
         <v>65</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>44</v>
@@ -3254,13 +3252,13 @@
         <v>66</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>44</v>
@@ -3271,13 +3269,13 @@
         <v>67</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>44</v>
@@ -3288,13 +3286,13 @@
         <v>68</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>44</v>
@@ -3305,13 +3303,13 @@
         <v>69</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>44</v>
@@ -3322,13 +3320,13 @@
         <v>70</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>44</v>
@@ -3339,13 +3337,13 @@
         <v>71</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>44</v>
@@ -3356,13 +3354,13 @@
         <v>72</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>44</v>
@@ -3373,13 +3371,13 @@
         <v>73</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>44</v>
@@ -3389,14 +3387,14 @@
       <c r="A77" s="18">
         <v>74</v>
       </c>
-      <c r="B77" s="27" t="s">
-        <v>168</v>
+      <c r="B77" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>44</v>
@@ -3407,13 +3405,13 @@
         <v>75</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>44</v>
@@ -3424,13 +3422,13 @@
         <v>76</v>
       </c>
       <c r="B79" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" s="21" t="s">
         <v>172</v>
-      </c>
-      <c r="C79" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D79" s="21" t="s">
-        <v>173</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>44</v>
@@ -3441,13 +3439,13 @@
         <v>77</v>
       </c>
       <c r="B80" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D80" s="21" t="s">
         <v>174</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D80" s="21" t="s">
-        <v>175</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>44</v>
@@ -3458,13 +3456,13 @@
         <v>78</v>
       </c>
       <c r="B81" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D81" s="21" t="s">
         <v>177</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D81" s="21" t="s">
-        <v>178</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>44</v>
@@ -3475,13 +3473,13 @@
         <v>79</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C82" s="21" t="s">
         <v>27</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>44</v>
@@ -3492,13 +3490,13 @@
         <v>80</v>
       </c>
       <c r="B83" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="21" t="s">
         <v>180</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D83" s="21" t="s">
-        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>44</v>
@@ -3509,13 +3507,13 @@
         <v>81</v>
       </c>
       <c r="B84" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" s="21" t="s">
         <v>182</v>
-      </c>
-      <c r="C84" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D84" s="21" t="s">
-        <v>183</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>44</v>
@@ -3526,13 +3524,13 @@
         <v>82</v>
       </c>
       <c r="B85" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="21" t="s">
         <v>184</v>
-      </c>
-      <c r="C85" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="D85" s="21" t="s">
-        <v>185</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>44</v>
@@ -3543,16 +3541,16 @@
         <v>83</v>
       </c>
       <c r="B86" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="D86" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C86" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="D86" s="21" t="s">
-        <v>188</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
